--- a/data/trans_dic/IP1014-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1014-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen defectos del habla</t>
+          <t>Menores que padecen defectos del habla (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,29</t>
+          <t>0,0; 3,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,93</t>
+          <t>0,0; 3,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,02</t>
+          <t>0,0; 4,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 2,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,89</t>
+          <t>0,0; 2,58</t>
         </is>
       </c>
     </row>
@@ -787,32 +788,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 1,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,17</t>
+          <t>0,14; 1,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,48</t>
+          <t>0,26; 1,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -822,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,95</t>
+          <t>0,15; 0,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,48</t>
+          <t>0,0; 0,44</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,14</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,19</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,11</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,24</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,53</t>
+          <t>0,0; 0,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,02</t>
+          <t>0,19; 1,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,27</t>
+          <t>0,26; 1,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,77</t>
+          <t>0,08; 0,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,62</t>
+          <t>0,1; 0,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,77</t>
+          <t>0,21; 0,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,42</t>
+          <t>0,04; 0,37</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen defectos del habla (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3505</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3225</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3518</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3401</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4515</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3421</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3307</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3275</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1333</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4170</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1333</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5234</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>680; 6205</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1267; 7916</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4700</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>676; 5528</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1378; 8531</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4250</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2213</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3819</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4163</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3666</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4069</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3399</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4691</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4041</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>6030</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2942</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4927</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1348; 7461</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1940; 9306</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>617; 5357</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1360; 8694</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>3088; 11253</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>615; 5343</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1014-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1014-Estudios-trans_dic.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,86</t>
+          <t>0,0; 3,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -693,32 +693,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,71</t>
+          <t>0,0; 3,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,21</t>
+          <t>0,0; 3,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,96</t>
+          <t>0,0; 5,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 2,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,58</t>
+          <t>0,0; 3,11</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,16</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,3</t>
+          <t>0,14; 1,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,61</t>
+          <t>0,25; 1,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,91</t>
+          <t>0,16; 1,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,44</t>
+          <t>0,0; 0,48</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,43</t>
+          <t>0,0; 0,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,32 +1023,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,03</t>
+          <t>0,18; 1,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,25</t>
+          <t>0,26; 1,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,72</t>
+          <t>0,08; 0,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,62</t>
+          <t>0,1; 0,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,77</t>
+          <t>0,2; 0,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,37</t>
+          <t>0,04; 0,41</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3505</t>
+          <t>0; 3229</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1321,32 +1321,32 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3225</t>
+          <t>0; 3098</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3518</t>
+          <t>0; 3119</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3401</t>
+          <t>0; 3457</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4515</t>
+          <t>0; 4526</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3421</t>
+          <t>0; 3641</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3307</t>
+          <t>0; 3975</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5234</t>
+          <t>0; 5702</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1484,32 +1484,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>680; 6205</t>
+          <t>679; 5751</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1267; 7916</t>
+          <t>1232; 7342</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4700</t>
+          <t>0; 4351</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>676; 5528</t>
+          <t>678; 5539</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1378; 8531</t>
+          <t>1473; 9401</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4250</t>
+          <t>0; 4611</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2213</t>
+          <t>0; 2537</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3819</t>
+          <t>0; 3380</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4163</t>
+          <t>0; 3937</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3666</t>
+          <t>0; 3368</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4069</t>
+          <t>0; 4154</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2942</t>
+          <t>0; 3026</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4927</t>
+          <t>0; 6325</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1810,32 +1810,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1348; 7461</t>
+          <t>1316; 7544</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1940; 9306</t>
+          <t>1968; 9095</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>617; 5357</t>
+          <t>619; 5246</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1360; 8694</t>
+          <t>1373; 8862</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3088; 11253</t>
+          <t>2898; 11057</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>615; 5343</t>
+          <t>617; 5873</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1014-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1014-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,55</t>
+          <t>0,0; 3,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 3,72</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 6,02</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,29</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,57</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,73</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,04</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,55</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,11</t>
+          <t>0,0; 2,89</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,34 +788,34 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,14; 1,17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0,25; 1,48</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,84</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,27</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,14; 1,21</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,25; 1,49</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,89</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
           <t>0,08; 0,62</t>
@@ -823,7 +823,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,0</t>
+          <t>0,15; 0,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -845,27 +845,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,27%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -898,27 +898,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,14</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,19</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,53</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,14</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 1,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,23</t>
+          <t>0,0; 1,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,44</t>
+          <t>0,18; 1,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,27; 1,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>0,08; 0,77</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,53</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,79</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,18; 1,04</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,26; 1,22</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,08; 0,7</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,63</t>
+          <t>0,13; 0,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,76</t>
+          <t>0,2; 0,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,41</t>
+          <t>0,04; 0,42</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1205,27 +1205,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1258,27 +1258,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>662</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3229</t>
+          <t>0; 3417</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0; 3110</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4131</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3901</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3098</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3119</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3457</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4526</t>
+          <t>0; 4472</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3641</t>
+          <t>0; 4242</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3975</t>
+          <t>0; 3697</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1363,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3275</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1333</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2084</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3275</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1333</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>678; 5584</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1236; 7294</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4107</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0; 5702</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4495</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>679; 5751</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1232; 7342</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0; 4351</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>678; 5539</t>
+          <t>677; 5559</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1473; 9401</t>
+          <t>1378; 8980</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4611</t>
+          <t>0; 4661</t>
         </is>
       </c>
     </row>
@@ -1526,22 +1526,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1579,27 +1579,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>443</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>793</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1632,27 +1632,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0; 3383</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3752</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2537</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3380</t>
-        </is>
-      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3937</t>
+          <t>0; 2143</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3368</t>
+          <t>0; 3677</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4154</t>
+          <t>0; 4182</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3399</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4691</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1339</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3399</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4691</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3026</t>
+          <t>1313; 7368</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6325</t>
+          <t>1995; 9527</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>594; 5701</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3590</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5560</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1316; 7544</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>1968; 9095</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>619; 5246</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1373; 8862</t>
+          <t>1755; 8679</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2898; 11057</t>
+          <t>2871; 11240</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>617; 5873</t>
+          <t>617; 6052</t>
         </is>
       </c>
     </row>
